--- a/assets/downloads/CotizacionPercy Sullca Tito.xlsx
+++ b/assets/downloads/CotizacionPercy Sullca Tito.xlsx
@@ -167,7 +167,7 @@
     <t>PRECIO UNIT. (SOLES)</t>
   </si>
   <si>
-    <t>PEPE</t>
+    <t>Arigato</t>
   </si>
   <si>
     <t>NOTAS:</t>
@@ -426,7 +426,7 @@
     <t>N.Proveedor</t>
   </si>
   <si>
-    <t>mini</t>
+    <t>dfgdfg</t>
   </si>
   <si>
     <t>N° Cajas</t>

--- a/assets/downloads/CotizacionPercy Sullca Tito.xlsx
+++ b/assets/downloads/CotizacionPercy Sullca Tito.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId4"/>
@@ -113,9 +113,9 @@
     <t>Hola Percy Sullca Tito 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $1.47312
+        ☑️Costo CBM: $445.5
         ☑️Impuestos: $499.56
-        ☑️ Total: $501.03312
+        ☑️ Total: $945.06
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -2103,7 +2103,7 @@
       <c r="I30" s="49"/>
       <c r="J30" s="49"/>
       <c r="K30" s="14" t="str">
-        <f>'2'!L7*J11</f>
+        <f>IF('2'!P7&lt;1, '2'!P7*J11, '2'!P7*J11)</f>
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">

--- a/assets/downloads/CotizacionPercy Sullca Tito.xlsx
+++ b/assets/downloads/CotizacionPercy Sullca Tito.xlsx
@@ -1752,8 +1752,9 @@
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="95">
-        <v>11.16</v>
+      <c r="J11" s="95" t="str">
+        <f>'2'!L7</f>
+        <v>0</v>
       </c>
       <c r="K11" s="73"/>
       <c r="L11" s="73"/>

--- a/assets/downloads/CotizacionPercy Sullca Tito.xlsx
+++ b/assets/downloads/CotizacionPercy Sullca Tito.xlsx
@@ -117,8 +117,8 @@
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
         ☑️Costo CBM: $445.5
-        ☑️Impuestos: $499.56
-        ☑️ Total: $945.06
+        ☑️Impuestos: $487.4
+        ☑️ Total: $932.9
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="83">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="O7" s="77" t="s">
         <v>19</v>

--- a/assets/downloads/CotizacionPercy Sullca Tito.xlsx
+++ b/assets/downloads/CotizacionPercy Sullca Tito.xlsx
@@ -71,7 +71,7 @@
     <t>TELEFONO:</t>
   </si>
   <si>
-    <t>972 896 791</t>
+    <t>51 906 118 935</t>
   </si>
   <si>
     <t>CLIENTE:</t>
@@ -116,9 +116,9 @@
     <t>Hola Percy Sullca Tito 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $445.5
-        ☑️Impuestos: $487.4
-        ☑️ Total: $932.9
+        ☑️Costo CBM: $0
+        ☑️Impuestos: $436.7
+        ☑️ Total: $436.7
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -3590,9 +3590,7 @@
       <c r="O7" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="77">
-        <v>375</v>
-      </c>
+      <c r="P7" s="77"/>
     </row>
     <row r="8" spans="1:16">
       <c r="B8" s="74" t="s">
@@ -3833,43 +3831,43 @@
         <v>106</v>
       </c>
       <c r="C14" s="81" t="str">
-        <f>ROUNDUP(L14*C13,2)</f>
+        <f>L14*C13</f>
         <v>0</v>
       </c>
       <c r="D14" s="81" t="str">
-        <f>ROUNDUP(L14*D13,2)</f>
+        <f>L14*D13</f>
         <v>0</v>
       </c>
       <c r="E14" s="81" t="str">
-        <f>ROUNDUP(L14*E13,2)</f>
+        <f>L14*E13</f>
         <v>0</v>
       </c>
       <c r="F14" s="81" t="str">
-        <f>ROUNDUP(L14*F13,2)</f>
+        <f>L14*F13</f>
         <v>0</v>
       </c>
       <c r="G14" s="81" t="str">
-        <f>ROUNDUP(L14*G13,2)</f>
+        <f>L14*G13</f>
         <v>0</v>
       </c>
       <c r="H14" s="81" t="str">
-        <f>ROUNDUP(L14*H13,2)</f>
+        <f>L14*H13</f>
         <v>0</v>
       </c>
       <c r="I14" s="81" t="str">
-        <f>ROUNDUP(L14*I13,2)</f>
+        <f>L14*I13</f>
         <v>0</v>
       </c>
       <c r="J14" s="81" t="str">
-        <f>ROUNDUP(L14*J13,2)</f>
+        <f>L14*J13</f>
         <v>0</v>
       </c>
       <c r="K14" s="81" t="str">
-        <f>ROUNDUP(L14*K13,2)</f>
+        <f>L14*K13</f>
         <v>0</v>
       </c>
       <c r="L14" s="86" t="str">
-        <f>IF(L7&lt;1, ROUNDUP(P7*0.6, 0), ROUNDUP(P7*0.6*L7, 0))</f>
+        <f>IF(L7&lt;1, P7*0.6, P7*0.6*L7)</f>
         <v>0</v>
       </c>
     </row>
@@ -3878,39 +3876,39 @@
         <v>107</v>
       </c>
       <c r="C15" s="81" t="str">
-        <f>ROUNDUP(C11+C14,2)</f>
+        <f>C11+C14</f>
         <v>0</v>
       </c>
       <c r="D15" s="81" t="str">
-        <f>ROUNDUP(D11+D14,2)</f>
+        <f>D11+D14</f>
         <v>0</v>
       </c>
       <c r="E15" s="81" t="str">
-        <f>ROUNDUP(E11+E14,2)</f>
+        <f>E11+E14</f>
         <v>0</v>
       </c>
       <c r="F15" s="81" t="str">
-        <f>ROUNDUP(F11+F14,2)</f>
+        <f>F11+F14</f>
         <v>0</v>
       </c>
       <c r="G15" s="81" t="str">
-        <f>ROUNDUP(G11+G14,2)</f>
+        <f>G11+G14</f>
         <v>0</v>
       </c>
       <c r="H15" s="81" t="str">
-        <f>ROUNDUP(H11+H14,2)</f>
+        <f>H11+H14</f>
         <v>0</v>
       </c>
       <c r="I15" s="81" t="str">
-        <f>ROUNDUP(I11+I14,2)</f>
+        <f>I11+I14</f>
         <v>0</v>
       </c>
       <c r="J15" s="81" t="str">
-        <f>ROUNDUP(J11+J14,2)</f>
+        <f>J11+J14</f>
         <v>0</v>
       </c>
       <c r="K15" s="81" t="str">
-        <f>ROUNDUP(K11+K14,2)</f>
+        <f>K11+K14</f>
         <v>0</v>
       </c>
       <c r="L15" s="86" t="str">
@@ -3923,39 +3921,39 @@
         <v>108</v>
       </c>
       <c r="C16" s="81" t="str">
-        <f>ROUNDUP(C12+C14,2)</f>
+        <f>C12+C14</f>
         <v>0</v>
       </c>
       <c r="D16" s="81" t="str">
-        <f>ROUNDUP(D12+D14,2)</f>
+        <f>D12+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="81" t="str">
-        <f>ROUNDUP(E12+E14,2)</f>
+        <f>E12+E14</f>
         <v>0</v>
       </c>
       <c r="F16" s="81" t="str">
-        <f>ROUNDUP(F12+F14,2)</f>
+        <f>F12+F14</f>
         <v>0</v>
       </c>
       <c r="G16" s="81" t="str">
-        <f>ROUNDUP(G12+G14,2)</f>
+        <f>G12+G14</f>
         <v>0</v>
       </c>
       <c r="H16" s="81" t="str">
-        <f>ROUNDUP(H12+H14,2)</f>
+        <f>H12+H14</f>
         <v>0</v>
       </c>
       <c r="I16" s="81" t="str">
-        <f>ROUNDUP(I12+I14,2)</f>
+        <f>I12+I14</f>
         <v>0</v>
       </c>
       <c r="J16" s="81" t="str">
-        <f>ROUNDUP(J12+J14,2)</f>
+        <f>J12+J14</f>
         <v>0</v>
       </c>
       <c r="K16" s="81" t="str">
-        <f>ROUNDUP(K12+K14,2)</f>
+        <f>K12+K14</f>
         <v>0</v>
       </c>
       <c r="L16" s="86" t="str">
@@ -3968,39 +3966,39 @@
         <v>109</v>
       </c>
       <c r="C17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*C13,2),ROUND(50*C13,2))</f>
+        <f>IF(L15&gt;5000,100*C13,50*C13)</f>
         <v>0</v>
       </c>
       <c r="D17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*D13,2),ROUND(50*D13,2))</f>
+        <f>IF(L15&gt;5000,100*D13,50*D13)</f>
         <v>0</v>
       </c>
       <c r="E17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*E13,2),ROUND(50*E13,2))</f>
+        <f>IF(L15&gt;5000,100*E13,50*E13)</f>
         <v>0</v>
       </c>
       <c r="F17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*F13,2),ROUND(50*F13,2))</f>
+        <f>IF(L15&gt;5000,100*F13,50*F13)</f>
         <v>0</v>
       </c>
       <c r="G17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*G13,2),ROUND(50*G13,2))</f>
+        <f>IF(L15&gt;5000,100*G13,50*G13)</f>
         <v>0</v>
       </c>
       <c r="H17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*H13,2),ROUND(50*H13,2))</f>
+        <f>IF(L15&gt;5000,100*H13,50*H13)</f>
         <v>0</v>
       </c>
       <c r="I17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*I13,2),ROUND(50*I13,2))</f>
+        <f>IF(L15&gt;5000,100*I13,50*I13)</f>
         <v>0</v>
       </c>
       <c r="J17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*J13,2),ROUND(50*J13,2))</f>
+        <f>IF(L15&gt;5000,100*J13,50*J13)</f>
         <v>0</v>
       </c>
       <c r="K17" s="81" t="str">
-        <f>IF(L15&gt;5000,ROUND(100*K13,2),ROUND(50*K13,2))</f>
+        <f>IF(L15&gt;5000,100*K13,50*K13)</f>
         <v>0</v>
       </c>
       <c r="L17" s="86" t="str">
@@ -4013,39 +4011,39 @@
         <v>110</v>
       </c>
       <c r="C18" s="81" t="str">
-        <f>ROUNDUP(C15+C17,2)</f>
+        <f>C15+C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="81" t="str">
-        <f>ROUNDUP(D15+D17,2)</f>
+        <f>D15+D17</f>
         <v>0</v>
       </c>
       <c r="E18" s="81" t="str">
-        <f>ROUNDUP(E15+E17,2)</f>
+        <f>E15+E17</f>
         <v>0</v>
       </c>
       <c r="F18" s="81" t="str">
-        <f>ROUNDUP(F15+F17,2)</f>
+        <f>F15+F17</f>
         <v>0</v>
       </c>
       <c r="G18" s="81" t="str">
-        <f>ROUNDUP(G15+G17,2)</f>
+        <f>G15+G17</f>
         <v>0</v>
       </c>
       <c r="H18" s="81" t="str">
-        <f>ROUNDUP(H15+H17,2)</f>
+        <f>H15+H17</f>
         <v>0</v>
       </c>
       <c r="I18" s="81" t="str">
-        <f>ROUNDUP(I15+I17,2)</f>
+        <f>I15+I17</f>
         <v>0</v>
       </c>
       <c r="J18" s="81" t="str">
-        <f>ROUNDUP(J15+J17,2)</f>
+        <f>J15+J17</f>
         <v>0</v>
       </c>
       <c r="K18" s="81" t="str">
-        <f>ROUNDUP(K15+K17,2)</f>
+        <f>K15+K17</f>
         <v>0</v>
       </c>
       <c r="L18" s="86" t="str">
@@ -4058,39 +4056,39 @@
         <v>111</v>
       </c>
       <c r="C19" s="81" t="str">
-        <f>ROUNDUP(C16+C17,2)</f>
+        <f>C16+C17</f>
         <v>0</v>
       </c>
       <c r="D19" s="81" t="str">
-        <f>ROUNDUP(D16+D17,2)</f>
+        <f>D16+D17</f>
         <v>0</v>
       </c>
       <c r="E19" s="81" t="str">
-        <f>ROUNDUP(E16+E17,2)</f>
+        <f>E16+E17</f>
         <v>0</v>
       </c>
       <c r="F19" s="81" t="str">
-        <f>ROUNDUP(F16+F17,2)</f>
+        <f>F16+F17</f>
         <v>0</v>
       </c>
       <c r="G19" s="81" t="str">
-        <f>ROUNDUP(G16+G17,2)</f>
+        <f>G16+G17</f>
         <v>0</v>
       </c>
       <c r="H19" s="81" t="str">
-        <f>ROUNDUP(H16+H17,2)</f>
+        <f>H16+H17</f>
         <v>0</v>
       </c>
       <c r="I19" s="81" t="str">
-        <f>ROUNDUP(I16+I17,2)</f>
+        <f>I16+I17</f>
         <v>0</v>
       </c>
       <c r="J19" s="81" t="str">
-        <f>ROUNDUP(J16+J17,2)</f>
+        <f>J16+J17</f>
         <v>0</v>
       </c>
       <c r="K19" s="81" t="str">
-        <f>ROUNDUP(K16+K17,2)</f>
+        <f>K16+K17</f>
         <v>0</v>
       </c>
       <c r="L19" s="86" t="str">
@@ -4449,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="81" t="str">
-        <f>IF(L7&lt;1, ROUNDUP(P7*0.4, 0), ROUNDUP(P7*0.4*L7, 0))</f>
+        <f>IF(L7&lt;1, P7*0.4,P7*0.4*L7)</f>
         <v>0</v>
       </c>
     </row>
@@ -4496,39 +4494,39 @@
         <v>118</v>
       </c>
       <c r="C44" s="81" t="str">
-        <f>SUM(C15,C40,C32,(C26*C10))</f>
+        <f>SUM(C15,C40,C32,(C26))</f>
         <v>0</v>
       </c>
       <c r="D44" s="81" t="str">
-        <f>SUM(D15,D40,D32,(D26*D10))</f>
+        <f>SUM(D15,D40,D32,(D26))</f>
         <v>0</v>
       </c>
       <c r="E44" s="81" t="str">
-        <f>SUM(E15,E40,E32,(E26*E10))</f>
+        <f>SUM(E15,E40,E32,(E26))</f>
         <v>0</v>
       </c>
       <c r="F44" s="81" t="str">
-        <f>SUM(F15,F40,F32,(F26*F10))</f>
+        <f>SUM(F15,F40,F32,(F26))</f>
         <v>0</v>
       </c>
       <c r="G44" s="81" t="str">
-        <f>SUM(G15,G40,G32,(G26*G10))</f>
+        <f>SUM(G15,G40,G32,(G26))</f>
         <v>0</v>
       </c>
       <c r="H44" s="81" t="str">
-        <f>SUM(H15,H40,H32,(H26*H10))</f>
+        <f>SUM(H15,H40,H32,(H26))</f>
         <v>0</v>
       </c>
       <c r="I44" s="81" t="str">
-        <f>SUM(I15,I40,I32,(I26*I10))</f>
+        <f>SUM(I15,I40,I32,(I26))</f>
         <v>0</v>
       </c>
       <c r="J44" s="81" t="str">
-        <f>SUM(J15,J40,J32,(J26*J10))</f>
+        <f>SUM(J15,J40,J32,(J26))</f>
         <v>0</v>
       </c>
       <c r="K44" s="81" t="str">
-        <f>SUM(K15,K40,K32,(K26*K10))</f>
+        <f>SUM(K15,K40,K32,(K26))</f>
         <v>0</v>
       </c>
       <c r="L44" s="81" t="str">
@@ -4574,39 +4572,39 @@
         <v>119</v>
       </c>
       <c r="C46" s="81" t="str">
-        <f>ROUND(SUM(C44/C45),2)</f>
+        <f>SUM(C44/C45)</f>
         <v>0</v>
       </c>
       <c r="D46" s="81" t="str">
-        <f>ROUND(SUM(D44/D45),2)</f>
+        <f>SUM(D44/D45)</f>
         <v>0</v>
       </c>
       <c r="E46" s="81" t="str">
-        <f>ROUND(SUM(E44/E45),2)</f>
+        <f>SUM(E44/E45)</f>
         <v>0</v>
       </c>
       <c r="F46" s="81" t="str">
-        <f>ROUND(SUM(F44/F45),2)</f>
+        <f>SUM(F44/F45)</f>
         <v>0</v>
       </c>
       <c r="G46" s="81" t="str">
-        <f>ROUND(SUM(G44/G45),2)</f>
+        <f>SUM(G44/G45)</f>
         <v>0</v>
       </c>
       <c r="H46" s="81" t="str">
-        <f>ROUND(SUM(H44/H45),2)</f>
+        <f>SUM(H44/H45)</f>
         <v>0</v>
       </c>
       <c r="I46" s="81" t="str">
-        <f>ROUND(SUM(I44/I45),2)</f>
+        <f>SUM(I44/I45)</f>
         <v>0</v>
       </c>
       <c r="J46" s="81" t="str">
-        <f>ROUND(SUM(J44/J45),2)</f>
+        <f>SUM(J44/J45)</f>
         <v>0</v>
       </c>
       <c r="K46" s="81" t="str">
-        <f>ROUND(SUM(K44/K45),2)</f>
+        <f>SUM(K44/K45)</f>
         <v>0</v>
       </c>
       <c r="L46" s="74"/>
@@ -4616,39 +4614,39 @@
         <v>120</v>
       </c>
       <c r="C47" s="85" t="str">
-        <f>ROUND(C46*3.7,2)</f>
+        <f>C46*3.7</f>
         <v>0</v>
       </c>
       <c r="D47" s="85" t="str">
-        <f>ROUND(D46*3.7,2)</f>
+        <f>D46*3.7</f>
         <v>0</v>
       </c>
       <c r="E47" s="85" t="str">
-        <f>ROUND(E46*3.7,2)</f>
+        <f>E46*3.7</f>
         <v>0</v>
       </c>
       <c r="F47" s="85" t="str">
-        <f>ROUND(F46*3.7,2)</f>
+        <f>F46*3.7</f>
         <v>0</v>
       </c>
       <c r="G47" s="85" t="str">
-        <f>ROUND(G46*3.7,2)</f>
+        <f>G46*3.7</f>
         <v>0</v>
       </c>
       <c r="H47" s="85" t="str">
-        <f>ROUND(H46*3.7,2)</f>
+        <f>H46*3.7</f>
         <v>0</v>
       </c>
       <c r="I47" s="85" t="str">
-        <f>ROUND(I46*3.7,2)</f>
+        <f>I46*3.7</f>
         <v>0</v>
       </c>
       <c r="J47" s="85" t="str">
-        <f>ROUND(J46*3.7,2)</f>
+        <f>J46*3.7</f>
         <v>0</v>
       </c>
       <c r="K47" s="85" t="str">
-        <f>ROUND(K46*3.7,2)</f>
+        <f>K46*3.7</f>
         <v>0</v>
       </c>
       <c r="L47" s="74"/>
